--- a/diseases/d071/1995-1999.xlsx
+++ b/diseases/d071/1995-1999.xlsx
@@ -1466,6 +1466,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1611,6 +1616,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1756,6 +1766,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1901,6 +1916,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2046,6 +2066,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2191,6 +2216,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2336,6 +2366,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2481,6 +2516,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2626,6 +2666,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2771,6 +2816,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2916,6 +2966,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3061,6 +3116,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3437,6 +3497,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3582,6 +3647,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3727,6 +3797,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3872,6 +3947,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4017,6 +4097,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4162,6 +4247,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4307,6 +4397,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4452,6 +4547,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4597,6 +4697,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4742,6 +4847,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4887,6 +4997,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5032,6 +5147,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5408,6 +5528,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5553,6 +5678,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5698,6 +5828,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5843,6 +5978,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5988,6 +6128,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6133,6 +6278,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6278,6 +6428,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6423,6 +6578,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6568,6 +6728,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6713,6 +6878,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6858,6 +7028,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7001,6 +7176,11 @@
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">

--- a/diseases/d071/1995-1999.xlsx
+++ b/diseases/d071/1995-1999.xlsx
@@ -1461,11 +1461,6 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1478,22 +1473,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1611,11 +1596,6 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1628,22 +1608,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1761,11 +1731,6 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1778,22 +1743,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1911,11 +1866,6 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1928,22 +1878,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -2061,11 +2001,6 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2078,22 +2013,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2211,11 +2136,6 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2228,22 +2148,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2361,11 +2271,6 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2378,22 +2283,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2511,11 +2406,6 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2528,22 +2418,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2661,11 +2541,6 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2678,22 +2553,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2811,11 +2676,6 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2828,22 +2688,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2961,11 +2811,6 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2978,22 +2823,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -3111,11 +2946,6 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3128,22 +2958,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3492,11 +3312,6 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3509,22 +3324,12 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3642,11 +3447,6 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3659,22 +3459,12 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3792,11 +3582,6 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3809,22 +3594,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3942,11 +3717,6 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3959,22 +3729,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -4092,11 +3852,6 @@
       <c r="Q22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4109,22 +3864,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4242,11 +3987,6 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4259,22 +3999,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4392,11 +4122,6 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4409,22 +4134,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4542,11 +4257,6 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4559,22 +4269,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4692,11 +4392,6 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4709,22 +4404,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4842,11 +4527,6 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4859,22 +4539,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4992,11 +4662,6 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5009,22 +4674,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -5142,11 +4797,6 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5159,22 +4809,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5523,11 +5163,6 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5540,22 +5175,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5673,11 +5298,6 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5690,22 +5310,12 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5823,11 +5433,6 @@
       <c r="Q33" t="n">
         <v>0</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5840,22 +5445,12 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5973,11 +5568,6 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5990,22 +5580,12 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -6123,11 +5703,6 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6140,22 +5715,12 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -6273,11 +5838,6 @@
       <c r="Q36" t="n">
         <v>0</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6290,22 +5850,12 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
-      </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -6423,11 +5973,6 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6440,22 +5985,12 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6573,11 +6108,6 @@
       <c r="Q38" t="n">
         <v>0</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6590,22 +6120,12 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
-      </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6723,11 +6243,6 @@
       <c r="Q39" t="n">
         <v>0</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6740,22 +6255,12 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
-      </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6873,11 +6378,6 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6890,22 +6390,12 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
-      </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -7023,11 +6513,6 @@
       <c r="Q41" t="n">
         <v>0</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7040,22 +6525,12 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
-      </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -7173,11 +6648,6 @@
       <c r="Q42" t="n">
         <v>0</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>missing_population</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7190,22 +6660,12 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
-      </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>

--- a/diseases/d071/1995-1999.xlsx
+++ b/diseases/d071/1995-1999.xlsx
@@ -1461,6 +1461,11 @@
       <c r="Q5" t="n">
         <v>0</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,12 +1478,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1596,6 +1611,11 @@
       <c r="Q6" t="n">
         <v>0</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1608,12 +1628,22 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1731,6 +1761,11 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1743,12 +1778,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1866,6 +1911,11 @@
       <c r="Q8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1878,12 +1928,22 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -2001,6 +2061,11 @@
       <c r="Q9" t="n">
         <v>0</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2013,12 +2078,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2136,6 +2211,11 @@
       <c r="Q10" t="n">
         <v>0</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2148,12 +2228,22 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2271,6 +2361,11 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2283,12 +2378,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2406,6 +2511,11 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2418,12 +2528,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2541,6 +2661,11 @@
       <c r="Q13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2553,12 +2678,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2676,6 +2811,11 @@
       <c r="Q14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2688,12 +2828,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2811,6 +2961,11 @@
       <c r="Q15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2823,12 +2978,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2946,6 +3111,11 @@
       <c r="Q16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2958,12 +3128,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3312,6 +3492,11 @@
       <c r="Q18" t="n">
         <v>0</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3324,12 +3509,22 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
@@ -3447,6 +3642,11 @@
       <c r="Q19" t="n">
         <v>0</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3459,12 +3659,22 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
@@ -3582,6 +3792,11 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3594,12 +3809,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3717,6 +3942,11 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3729,12 +3959,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3852,6 +4092,11 @@
       <c r="Q22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3864,12 +4109,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3987,6 +4242,11 @@
       <c r="Q23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3999,12 +4259,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4122,6 +4392,11 @@
       <c r="Q24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4134,12 +4409,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4257,6 +4542,11 @@
       <c r="Q25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4269,12 +4559,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4392,6 +4692,11 @@
       <c r="Q26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4404,12 +4709,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4527,6 +4842,11 @@
       <c r="Q27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4539,12 +4859,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4662,6 +4992,11 @@
       <c r="Q28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4674,12 +5009,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4797,6 +5142,11 @@
       <c r="Q29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4809,12 +5159,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5163,6 +5523,11 @@
       <c r="Q31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5175,12 +5540,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
@@ -5298,6 +5673,11 @@
       <c r="Q32" t="n">
         <v>0</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5310,12 +5690,22 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
@@ -5433,6 +5823,11 @@
       <c r="Q33" t="n">
         <v>0</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5445,12 +5840,22 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
@@ -5568,6 +5973,11 @@
       <c r="Q34" t="n">
         <v>0</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5580,12 +5990,22 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
@@ -5703,6 +6123,11 @@
       <c r="Q35" t="n">
         <v>0</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5715,12 +6140,22 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
@@ -5838,6 +6273,11 @@
       <c r="Q36" t="n">
         <v>0</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5850,12 +6290,22 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
@@ -5973,6 +6423,11 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5985,12 +6440,22 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
@@ -6108,6 +6573,11 @@
       <c r="Q38" t="n">
         <v>0</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6120,12 +6590,22 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
@@ -6243,6 +6723,11 @@
       <c r="Q39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6255,12 +6740,22 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
@@ -6378,6 +6873,11 @@
       <c r="Q40" t="n">
         <v>0</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6390,12 +6890,22 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV40" t="inlineStr">
         <is>
@@ -6513,6 +7023,11 @@
       <c r="Q41" t="n">
         <v>0</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6525,12 +7040,22 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV41" t="inlineStr">
         <is>
@@ -6648,6 +7173,11 @@
       <c r="Q42" t="n">
         <v>0</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6660,12 +7190,22 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
